--- a/ig/TEST-SUPPLEMENT/ValueSet-JDV-J238-TypeOffre-ROR.xlsx
+++ b/ig/TEST-SUPPLEMENT/ValueSet-JDV-J238-TypeOffre-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="575">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="585">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250828120000</t>
+    <t>20251017120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-28T12:00:00+01:00</t>
+    <t>2025-10-17T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -126,7 +126,7 @@
     <t>05</t>
   </si>
   <si>
-    <t>Centre d'Accueil Thérapeutique à Temps Partiel (CATTP)</t>
+    <t>Centre d’Activités Thérapeutiques et de Temps de Groupe (CATTG) – ex CATTP</t>
   </si>
   <si>
     <t>06</t>
@@ -156,7 +156,7 @@
     <t>10</t>
   </si>
   <si>
-    <t>Centre Médico-Psychologique (CMP)</t>
+    <t>Centre Médico-Psychologique (CMP) Adulte</t>
   </si>
   <si>
     <t>11</t>
@@ -366,7 +366,7 @@
     <t>46</t>
   </si>
   <si>
-    <t>Établissement et Service de Pré-Orientation (ESPO)</t>
+    <t>Établissement et Service de Préorientation (ESPO)</t>
   </si>
   <si>
     <t>47</t>
@@ -1116,7 +1116,7 @@
     <t>174</t>
   </si>
   <si>
-    <t>Unité psychiatrique</t>
+    <t>Unité hospitalière de psychiatrie de l’adulte</t>
   </si>
   <si>
     <t>175</t>
@@ -1602,7 +1602,7 @@
     <t>257</t>
   </si>
   <si>
-    <t>Unité pour Personnes Handicapées Vieillissantes (UPHV)</t>
+    <t>Unité pour Personnes Handicapées Vieillissantes (UPHV - UPHA)</t>
   </si>
   <si>
     <t>258</t>
@@ -1729,6 +1729,36 @@
   </si>
   <si>
     <t>Unité Hospitalière de Courte Durée (UHCD)</t>
+  </si>
+  <si>
+    <t>279</t>
+  </si>
+  <si>
+    <t>Equipe mobile de psychiatrie de l'Enfant et de l'Adolescent</t>
+  </si>
+  <si>
+    <t>280</t>
+  </si>
+  <si>
+    <t>Equipe mobile de psychiatrie adulte</t>
+  </si>
+  <si>
+    <t>281</t>
+  </si>
+  <si>
+    <t>Centre Médico-Psychologique Enfant et Adolescent (CMPEA)</t>
+  </si>
+  <si>
+    <t>282</t>
+  </si>
+  <si>
+    <t>Unité hospitalière de psychiatrie de l’enfant et de l’adolescent (pédopsychiatrie)</t>
+  </si>
+  <si>
+    <t>283</t>
+  </si>
+  <si>
+    <t>Equipe mobile de psychiatrie périnatale</t>
   </si>
   <si>
     <t/>
@@ -1999,7 +2029,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B275"/>
+  <dimension ref="A1:B280"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -4195,15 +4225,55 @@
         <v>572</v>
       </c>
       <c r="B274" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B275" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="B276" t="s" s="2">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="B277" t="s" s="2">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="B278" t="s" s="2">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="B279" t="s" s="2">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="B280" t="s" s="2">
+        <v>584</v>
       </c>
     </row>
   </sheetData>
